--- a/output/full_scan/batch_seq6_2026-10-07.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-07.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6209</v>
+        <v>6278</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>908.7835076789396</v>
+        <v>1278.591960197977</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>250.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.91853686270434</v>
+        <v>78.57029280962662</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33.98240663554326</v>
+        <v>31.60010947739841</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.91087511431485</v>
+        <v>2.959196019797705</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.9449078318253444</v>
+        <v>3.86466853391542</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6278</v>
+        <v>6209</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>893.5919601979771</v>
+        <v>1188.78350767894</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>250.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>78.57029281697795</v>
+        <v>69.91853686787675</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.60010944970101</v>
+        <v>33.98240654127191</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.959196019797705</v>
+        <v>1.91087511431485</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3.864668534026668</v>
+        <v>0.9449078320367624</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6233</v>
+        <v>6191</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>815.7907753350966</v>
+        <v>1114.61176397452</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>24.95</v>
+        <v>87.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>80.67183097620284</v>
+        <v>64.05972957422684</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.27583771619281</v>
+        <v>17.92418729201374</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.179077533509653</v>
+        <v>1.561176397451972</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4474934988162743</v>
+        <v>0.6468804204078786</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6442</v>
+        <v>6271</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>812.8427394569317</v>
+        <v>1092.343820083011</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1815</v>
+        <v>241.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,29 +711,29 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.79114956076688</v>
+        <v>66.47847604522235</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.94150673162635</v>
+        <v>28.64389253984024</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.803703326024254</v>
+        <v>1.183221858007197</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>20.7787071735517</v>
+        <v>0.5861666050907459</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>810.3646574337215</v>
+        <v>1090.364657433722</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>371</v>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>77.03567568510098</v>
+        <v>77.0356756794053</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23.50766855804359</v>
+        <v>23.50766851305765</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.136465743372151</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>6.07890359830473</v>
+        <v>6.078903598749806</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6263</v>
+        <v>6442</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>807.0522383017537</v>
+        <v>1022.842739456933</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>178</v>
+        <v>1815</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.4901511722024</v>
+        <v>63.79114958426884</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.59003258286426</v>
+        <v>17.94150670527659</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.805223830175373</v>
+        <v>1.803703326024254</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.270423524517781</v>
+        <v>20.77870718178576</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6216</v>
+        <v>6233</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>806.0755393311467</v>
+        <v>985.7907753350966</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.25</v>
+        <v>24.95</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>65.29238378923102</v>
+        <v>80.6718309458782</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>34.34340093194228</v>
+        <v>34.27583769566554</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.371636076337888</v>
+        <v>3.179077533509653</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2073641393207241</v>
+        <v>0.4474934989386731</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6285</v>
+        <v>6263</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>789.1629774958244</v>
+        <v>977.0522383017536</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>257.5</v>
+        <v>178</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.49568277046458</v>
+        <v>70.49015115826607</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>19.44093213175377</v>
+        <v>23.590032583057</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.516297749582443</v>
+        <v>3.805223830175373</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.51865415748265</v>
+        <v>2.270423524295229</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6175</v>
+        <v>6187</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>767.6396045670371</v>
+        <v>950.2049110773154</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>77</v>
+        <v>1535</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.66783200846177</v>
+        <v>70.1374193660014</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.5500321547087</v>
+        <v>23.30897398331152</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.919931630282448</v>
+        <v>0.9952174847993236</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.16509913965281</v>
+        <v>30.11134760145118</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6271</v>
+        <v>6285</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>757.343820083011</v>
+        <v>949.1629774958244</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>241.5</v>
+        <v>257.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.47847606078827</v>
+        <v>65.495682745566</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.64389253984024</v>
+        <v>19.44093216478983</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.183221858007197</v>
+        <v>2.516297749582443</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5861666047569347</v>
+        <v>3.518654158261542</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6187</v>
+        <v>6216</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>750.2049110773158</v>
+        <v>946.0755393311468</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1535</v>
+        <v>21.25</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>70.13741935731768</v>
+        <v>65.29238373941941</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23.30897405659531</v>
+        <v>34.34340093253594</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9952174847993236</v>
+        <v>4.371636076337888</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>30.11134760122835</v>
+        <v>0.2073641393541084</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6218</v>
+        <v>6175</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>749.9306212566562</v>
+        <v>937.6396045670476</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60.8</v>
+        <v>77</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.3967697782511</v>
+        <v>60.66783200016373</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45.31293848464817</v>
+        <v>20.55003206708684</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.221328269451802</v>
+        <v>2.919931630282448</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.5848115948092127</v>
+        <v>1.165099140364939</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6226</v>
+        <v>6257</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>747.9227300064031</v>
+        <v>910.8908107554604</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>43.45</v>
+        <v>278</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.13117145391447</v>
+        <v>71.15678324319822</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>49.62371914150764</v>
+        <v>32.32500342397127</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6724666269292439</v>
+        <v>2.848902125883764</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.515335568110852</v>
+        <v>4.258379898868025</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6191</v>
+        <v>6456</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>719.6117639745197</v>
+        <v>892.8355463706955</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>87.5</v>
+        <v>102</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.05973006375729</v>
+        <v>77.08242956756888</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>17.92418716449944</v>
+        <v>36.65312059093638</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.561176397451972</v>
+        <v>4.383554637069555</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.646880419183902</v>
+        <v>2.837570013508282</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6227</v>
+        <v>6196</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>716.1116500238069</v>
+        <v>866.8631342960508</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>140.5</v>
+        <v>670</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>64.26691434297477</v>
+        <v>74.38666387790184</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>42.13604532356584</v>
+        <v>33.99195973970976</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3890446349770714</v>
+        <v>0.6996817283181594</v>
       </c>
       <c r="K16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.6816752320960351</v>
+        <v>14.31874230402713</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6432</v>
+        <v>6274</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>708.7360938090013</v>
+        <v>856.6372391378582</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>66.2</v>
+        <v>1720</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.53207813681011</v>
+        <v>66.56370560870039</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.67103974208789</v>
+        <v>23.80603173575937</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.662354909258429</v>
+        <v>1.289997375504728</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.282383968749394</v>
+        <v>38.36255933531625</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6168</v>
+        <v>6227</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>703.3573133892176</v>
+        <v>856.1116500238069</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.45</v>
+        <v>140.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.96385362216781</v>
+        <v>64.26691430096605</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>53.30703087147086</v>
+        <v>42.13604535486612</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7644031932233469</v>
+        <v>0.3890446349770714</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0508587111063825</v>
+        <v>0.6816752323408268</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6456</v>
+        <v>6449</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>702.8355463706955</v>
+        <v>833.5374255973968</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>102</v>
+        <v>261.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>77.08242955484192</v>
+        <v>67.218582000426</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>36.65312056859728</v>
+        <v>15.83360374389394</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.383554637069555</v>
+        <v>4.453742559739677</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.837570013374761</v>
+        <v>5.328363500996044</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6274</v>
+        <v>6432</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>686.6372391378583</v>
+        <v>823.7360938090014</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1720</v>
+        <v>66.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>66.56370559971899</v>
+        <v>56.53207818234639</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23.80603178712498</v>
+        <v>24.67103997795161</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.289997375504728</v>
+        <v>1.662354909258429</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>38.36255933275702</v>
+        <v>1.282383968404452</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6205</v>
+        <v>6174</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>685.5897834010601</v>
+        <v>820.0429778723528</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.74849973136905</v>
+        <v>68.01129277514299</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.66488442355971</v>
+        <v>24.92294422000739</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4737698637447416</v>
+        <v>5.234874668534547</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4968748972398811</v>
+        <v>1.630569023927008</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6472</v>
+        <v>6213</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>679.5147882921286</v>
+        <v>805.120160418574</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>428</v>
+        <v>796</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.12517972961543</v>
+        <v>83.65901605745668</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.15260078398156</v>
+        <v>34.54138202453218</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9946724692391596</v>
+        <v>0.8310151943672535</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,11 +1630,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1331425555885009</v>
+        <v>23.36514550107985</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>672.360361299631</v>
+        <v>787.3603612996325</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>41.8</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.33221075842252</v>
+        <v>62.33221084326555</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.83986039589363</v>
+        <v>24.83986043569337</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.720008832662141</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3155244954327467</v>
+        <v>0.3155244950989294</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6245</v>
+        <v>6214</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>668.6201660968308</v>
+        <v>776.8684288050279</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>87.3</v>
+        <v>189.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.88214411770866</v>
+        <v>63.25652752309372</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.74250218399412</v>
+        <v>27.28826159047423</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4177050397660287</v>
+        <v>0.3951600713322786</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1866610018826922</v>
+        <v>-1.326343397358352</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6207</v>
+        <v>6239</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>667.0245746113027</v>
+        <v>757.7817278490573</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>147.5</v>
+        <v>307.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>66.24013709530693</v>
+        <v>61.31873498780173</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.69238176790107</v>
+        <v>17.72883237917516</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.021934972306028</v>
+        <v>0.9917335383969936</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.004463215239692</v>
+        <v>2.734635060674005</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6290</v>
+        <v>6204</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>666.9627781320648</v>
+        <v>753.0974083427915</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>284.5</v>
+        <v>111.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.45632473488467</v>
+        <v>64.13753879292</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.91287153219594</v>
+        <v>31.01450514706403</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.249530052186183</v>
+        <v>0.8418229213768854</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3021235481132862</v>
+        <v>0.7805154104114846</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6275</v>
+        <v>6218</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>642.0702062003573</v>
+        <v>749.9306212566562</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>47.35</v>
+        <v>60.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.13802091789184</v>
+        <v>60.39676979006795</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>35.54736880585324</v>
+        <v>45.312938470897</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8403667880853908</v>
+        <v>1.221328269451802</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1587530503548899</v>
+        <v>-0.5848115948648571</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6438</v>
+        <v>6226</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>638.9282819613828</v>
+        <v>747.9227300064031</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>165.5</v>
+        <v>43.45</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.34942760876444</v>
+        <v>60.13117145102868</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.2871094231574</v>
+        <v>49.62371916452079</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.022153367176876</v>
+        <v>0.6724666269292439</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.482843006606787</v>
+        <v>-0.5153355680885925</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6257</v>
+        <v>6415</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>635.8908107554603</v>
+        <v>729.9139522505825</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>278</v>
+        <v>456.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>71.15678324523098</v>
+        <v>59.99513503107651</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.32500347316641</v>
+        <v>12.91681505054542</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.848902125883764</v>
+        <v>0.948500798147258</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>4.258379898823534</v>
+        <v>5.495724419993805</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6449</v>
+        <v>6190</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>633.5374255973968</v>
+        <v>724.7343796501179</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>261.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>67.21858200995064</v>
+        <v>66.99060181039019</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.83360378274136</v>
+        <v>21.46365587923608</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>4.453742559739677</v>
+        <v>1.3090790555532</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>5.328363501329859</v>
+        <v>0.9461863962129088</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6292</v>
+        <v>6194</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>627.661334672867</v>
+        <v>712.9718262273235</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>68.8</v>
+        <v>31.85</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.19404953404739</v>
+        <v>72.51138047589561</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35.74353931209077</v>
+        <v>24.46230478108398</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6863359432373225</v>
+        <v>1.397182622732349</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1631667395175235</v>
+        <v>0.1456402555742981</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6174</v>
+        <v>6205</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>620.0429778723528</v>
+        <v>705.5897834010601</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>58.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>68.01129277014297</v>
+        <v>58.74849969705934</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.9229442414547</v>
+        <v>31.66488437821849</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.234874668534547</v>
+        <v>0.4737698637447416</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,48 +2160,48 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.630569023938137</v>
+        <v>0.4968748973400245</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6173</v>
+        <v>6168</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>615.0404335329927</v>
+        <v>703.3573133892176</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>284</v>
+        <v>41.45</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.81417153291177</v>
+        <v>58.96385363092124</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>38.46113774162085</v>
+        <v>53.30703088383307</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2894454963500344</v>
+        <v>0.7644031932233469</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-4.757904489469507</v>
+        <v>0.0508587111620215</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6204</v>
+        <v>6202</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>613.0974083427934</v>
+        <v>701.7812845296538</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>111.5</v>
+        <v>60.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.13753878632103</v>
+        <v>57.86430410670783</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>31.01450512019213</v>
+        <v>18.014982783043</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8418229213768854</v>
+        <v>0.9896149706926152</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7805154105672507</v>
+        <v>0.549677456375166</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6213</v>
+        <v>6225</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>605.120160418574</v>
+        <v>690.4530490583022</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>796</v>
+        <v>68.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>83.65901605428601</v>
+        <v>60.97973693850414</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.54138207108637</v>
+        <v>23.63518025909653</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8310151943672535</v>
+        <v>0.5240011458490156</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>23.36514549963334</v>
+        <v>0.6012797028276093</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6423</v>
+        <v>6472</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>602.3327403153105</v>
+        <v>679.5147882921291</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>87.09999999999999</v>
+        <v>428</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.20194593846369</v>
+        <v>53.12517947588549</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.7918212253503</v>
+        <v>28.15260106778106</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7589823078233422</v>
+        <v>0.9946724692391596</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2575960395102536</v>
+        <v>0.1331425615971948</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6416</v>
+        <v>6245</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>599.6485501617767</v>
+        <v>668.6201660968308</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>118</v>
+        <v>87.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.74493338478728</v>
+        <v>55.88214405846502</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>33.9263535360336</v>
+        <v>31.74250210168358</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6656621705304919</v>
+        <v>0.4177050397660287</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.3362375528440298</v>
+        <v>0.1866610022165205</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6190</v>
+        <v>6207</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>584.7343796501301</v>
+        <v>667.0245746113026</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>147.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>66.99060167610301</v>
+        <v>66.24013710163548</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.4636557522912</v>
+        <v>32.69238172730899</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.3090790555532</v>
+        <v>1.021934972306028</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.9461863966357345</v>
+        <v>3.004463215184049</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6224</v>
+        <v>6290</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>581.7029256135392</v>
+        <v>666.9627781320647</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>80.2</v>
+        <v>284.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.44069972361162</v>
+        <v>60.45632467068936</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.24516257621973</v>
+        <v>31.91287158067573</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7287685718473859</v>
+        <v>1.249530052186183</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.309901959762302</v>
+        <v>0.3021235493372884</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6166</v>
+        <v>6438</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>579.8381987977805</v>
+        <v>648.9282819613832</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>131</v>
+        <v>165.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.71757880058118</v>
+        <v>66.34942753094239</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.13207268443682</v>
+        <v>32.28710943188091</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6037277013475145</v>
+        <v>1.022153367176876</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.341670659240846</v>
+        <v>1.482843008498399</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6194</v>
+        <v>6189</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>572.9718262273235</v>
+        <v>644.9323642575278</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>31.85</v>
+        <v>49.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>72.51138053368079</v>
+        <v>56.2246402301008</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>24.46230487923626</v>
+        <v>22.81787820085975</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.397182622732349</v>
+        <v>0.361265463895748</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.1456402554519051</v>
+        <v>0.1661675772247305</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6426</v>
+        <v>6275</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>572.1820619597542</v>
+        <v>642.0702062003573</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>347.5</v>
+        <v>47.35</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.85511727669489</v>
+        <v>59.13802051873153</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>39.52365962049682</v>
+        <v>35.54736872454369</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6590347441840546</v>
+        <v>0.8403667880853908</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-5.282924879971429</v>
+        <v>0.1587530510781512</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6196</v>
+        <v>6292</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>566.1536103760327</v>
+        <v>627.661334672867</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>670</v>
+        <v>68.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>74.38666391016889</v>
+        <v>59.19404948603572</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>33.99195973970976</v>
+        <v>35.743539091137</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6520945028763317</v>
+        <v>0.6863359432373225</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>14.31874230347076</v>
+        <v>0.1631667397623217</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6182</v>
+        <v>6284</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>564.5484611933429</v>
+        <v>618.0366693912142</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>63.53660557810738</v>
+        <v>55.60983356081118</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.70840923215798</v>
+        <v>15.70145753184652</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9542630259335008</v>
+        <v>1.483073435618746</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1</v>
@@ -2796,48 +2796,48 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.910147638922567</v>
+        <v>0.6195242915338481</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6214</v>
+        <v>6173</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>561.8684288050277</v>
+        <v>615.0404335329927</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>189.5</v>
+        <v>284</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>63.2565276096119</v>
+        <v>51.81417153322085</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>27.28826159833894</v>
+        <v>38.46113768261758</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3951600713322786</v>
+        <v>0.2894454963500344</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.326343397358352</v>
+        <v>-4.757904489373374</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6415</v>
+        <v>6419</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>559.9139522505824</v>
+        <v>613.6372548922902</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>456.5</v>
+        <v>165</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.99513509668756</v>
+        <v>59.36385152612709</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12.91681509008345</v>
+        <v>19.787965276597</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.948500798147258</v>
+        <v>1.525796667127343</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>5.495724419103538</v>
+        <v>1.762892163713766</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6202</v>
+        <v>6423</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>556.7812845296543</v>
+        <v>602.3327403153099</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>60.9</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.86430411308086</v>
+        <v>53.20194585068237</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.01498286310219</v>
+        <v>25.7918213824082</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.9896149706926152</v>
+        <v>0.7589823078233422</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5496774562750193</v>
+        <v>0.257596040088873</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6225</v>
+        <v>6416</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>520.4530490583022</v>
+        <v>599.6485501617767</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>68.7</v>
+        <v>118</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>60.9797369421299</v>
+        <v>57.7449333243862</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.635180265114</v>
+        <v>33.92635350337375</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5240011458490156</v>
+        <v>0.6656621705304919</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.6012797026050647</v>
+        <v>-0.3362375524879528</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6291</v>
+        <v>6224</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>515.5855476659409</v>
+        <v>581.7029256135392</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>469.5</v>
+        <v>80.2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.91468574536189</v>
+        <v>49.44069972227444</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.67807573151562</v>
+        <v>31.24516257844285</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.38995457060148</v>
+        <v>0.7287685718473859</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>1</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-6.157092427353589</v>
+        <v>-1.309901959695526</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6284</v>
+        <v>6166</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>503.0366693912133</v>
+        <v>579.8381987977804</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.60983355667622</v>
+        <v>59.7175787923069</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.70145750551865</v>
+        <v>27.13207266322777</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.483073435618746</v>
+        <v>0.6037277013475145</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>1</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.6195242916228632</v>
+        <v>1.341670659307622</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6239</v>
+        <v>6426</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>502.7817278490573</v>
+        <v>572.1820619597542</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>307.5</v>
+        <v>347.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>61.31873500661096</v>
+        <v>56.8551172669986</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.7288324974796</v>
+        <v>39.52365967365353</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9917335383969936</v>
+        <v>0.6590347441840546</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.734635060562739</v>
+        <v>-5.282924879348347</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6451</v>
+        <v>6208</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>501.2226613747974</v>
+        <v>569.8965647598603</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>426.5</v>
+        <v>79.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.70656254416125</v>
+        <v>57.2354225600587</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8.008262749745928</v>
+        <v>17.88257356394276</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9057174578493872</v>
+        <v>0.740048156085291</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.112877338068388</v>
+        <v>0.914523053211399</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6419</v>
+        <v>6182</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>498.6372548922904</v>
+        <v>564.5484611933429</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>59.36385162263648</v>
+        <v>63.53660557011811</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.78796527947836</v>
+        <v>25.70840922665987</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.525796667127343</v>
+        <v>0.9542630259335008</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.762892163580214</v>
+        <v>1.910147639111705</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6265</v>
+        <v>6259</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>495.5550318639356</v>
+        <v>563.8786841580572</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>49.15</v>
+        <v>32.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.87979619287865</v>
+        <v>63.65354111952311</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.37258279101757</v>
+        <v>18.99320220687035</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4743688620007186</v>
+        <v>1.980444476714285</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2233320327535053</v>
+        <v>0.5187660828140268</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6210</v>
+        <v>6230</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>483.0313365209965</v>
+        <v>530.387279350788</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>17.9</v>
+        <v>115.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.07529294057093</v>
+        <v>57.79831851633283</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3.58738910999716</v>
+        <v>17.59822310565456</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4558838171913005</v>
+        <v>1.34348626090824</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0882552645468249</v>
+        <v>0.4349750623642864</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6165</v>
+        <v>6164</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>482.2759528979984</v>
+        <v>524.3494522011297</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>47.75</v>
+        <v>13.35</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.6961889758693</v>
+        <v>64.8781802927614</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15.35058350426777</v>
+        <v>30.46784231376536</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>4.481579300156223</v>
+        <v>0.8458273144833002</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1133239852194509</v>
+        <v>0.1772137283206923</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6417</v>
+        <v>6291</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>475.1762968776478</v>
+        <v>515.5855476659409</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>105.5</v>
+        <v>469.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.57618252395608</v>
+        <v>49.91468571903499</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>35.15335466300403</v>
+        <v>24.67807571113032</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4036921631667138</v>
+        <v>0.38995457060148</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.6598419109939704</v>
+        <v>-6.157092426240912</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6462</v>
+        <v>6266</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>461.3979260777337</v>
+        <v>513.2768919722433</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>102</v>
+        <v>26.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.18175080998429</v>
+        <v>67.01235171385471</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.28160197502249</v>
+        <v>17.68325240216635</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8762478174881075</v>
+        <v>0.8276891972243356</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.4243380505607487</v>
+        <v>0.2023929483276068</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6189</v>
+        <v>6451</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>459.9323642575259</v>
+        <v>501.2226613747975</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>49.4</v>
+        <v>426.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>56.22464049846421</v>
+        <v>49.70656251561449</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.8178781698537</v>
+        <v>8.008262769837293</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.361265463895748</v>
+        <v>0.9057174578493872</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1661675770912047</v>
+        <v>1.112877338736043</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6208</v>
+        <v>6265</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>454.8965647598602</v>
+        <v>495.5550318639356</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>79.8</v>
+        <v>49.15</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>57.2354225600587</v>
+        <v>44.87979620518048</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.88257342240153</v>
+        <v>17.37258278630804</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.740048156085291</v>
+        <v>0.4743688620007186</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.914523052899829</v>
+        <v>0.2233320326756187</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6270</v>
+        <v>6210</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>453.079665110101</v>
+        <v>483.0313365209965</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>29.9</v>
+        <v>17.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.92853756450004</v>
+        <v>52.07529293850437</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.48591662205578</v>
+        <v>3.587389108847524</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7591000907020824</v>
+        <v>0.4558838171913005</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.167086127800006</v>
+        <v>0.0882552645468249</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6411</v>
+        <v>6165</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>444.000533513304</v>
+        <v>482.2759528979983</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>78.7</v>
+        <v>47.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.01954669697184</v>
+        <v>43.69618898677442</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8.299138467831192</v>
+        <v>15.35058344864762</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9776392885476703</v>
+        <v>4.481579300156223</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1702601500420492</v>
+        <v>-0.1133239851081739</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>426.4494411589886</v>
+        <v>475.176296877648</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>395</v>
+        <v>105.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.19517638874049</v>
+        <v>52.57618261777177</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.09523006885761</v>
+        <v>35.15335469268182</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5199582843049633</v>
+        <v>0.4036921631667138</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>4.141291978000842</v>
+        <v>0.6598419107714353</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6170</v>
+        <v>6277</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>424.5466270768386</v>
+        <v>462.5105222935029</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>49.15</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>59.82175756450914</v>
+        <v>50.32779066844415</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.06056082867982</v>
+        <v>12.44131717029223</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7940669262318061</v>
+        <v>0.5499145114771895</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0726196093354041</v>
+        <v>0.0756310311308203</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6259</v>
+        <v>6462</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>423.8786841580573</v>
+        <v>461.3979260777336</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>32.7</v>
+        <v>102</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>63.65354109642649</v>
+        <v>52.18175048560077</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.99320221173205</v>
+        <v>20.28160208755311</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.980444476714285</v>
+        <v>0.8762478174881075</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.5187660828696612</v>
+        <v>0.4243380520072657</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6230</v>
+        <v>6270</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>420.3872793507807</v>
+        <v>453.079665110101</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>115.5</v>
+        <v>29.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.79831903564653</v>
+        <v>51.92853753879945</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.59822310719968</v>
+        <v>21.48591669321407</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.34348626090824</v>
+        <v>0.7591000907020824</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.4349750603614007</v>
+        <v>0.1670861278779006</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6464</v>
+        <v>6411</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>408.6469690076021</v>
+        <v>444.000533513304</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.73771225024502</v>
+        <v>50.01954659951628</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23.23611576927393</v>
+        <v>8.299138425146193</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3490207061623582</v>
+        <v>0.9776392885476703</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0545077223590684</v>
+        <v>0.1702601503536057</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6269</v>
+        <v>6223</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>404.7219608169293</v>
+        <v>441.2364123052852</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>65.3</v>
+        <v>5530</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.76824636519937</v>
+        <v>51.14094903503386</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.92134060593834</v>
+        <v>12.27041424348824</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3475839359103814</v>
+        <v>0.8820010985153808</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0529605074628916</v>
+        <v>25.54717962325227</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6418</v>
+        <v>6414</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>403.6595016422124</v>
+        <v>436.4494411589886</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>34.35</v>
+        <v>395</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.11611109288328</v>
+        <v>52.19517623521183</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>31.32351561115382</v>
+        <v>19.09523007053111</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6413333463951123</v>
+        <v>0.5199582843049633</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1532982071414383</v>
+        <v>4.141291979781228</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6266</v>
+        <v>6269</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>398.2768919722433</v>
+        <v>424.7219608169293</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>26.4</v>
+        <v>65.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>67.01235175392409</v>
+        <v>49.76824636072489</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.6832524203893</v>
+        <v>12.92134057349342</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8276891972243356</v>
+        <v>0.3475839359103814</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2023929482497179</v>
+        <v>-0.0529605075296622</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6443</v>
+        <v>6170</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>394.7930425375959</v>
+        <v>424.5466270768388</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>27.6</v>
+        <v>49.15</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.41790379771669</v>
+        <v>59.82175765772524</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>29.21383403001946</v>
+        <v>19.06056082867982</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4616728907340448</v>
+        <v>0.7940669262318061</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2533259782828121</v>
+        <v>0.07261960935765439</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6164</v>
+        <v>6464</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>394.34945220113</v>
+        <v>408.6469690076021</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>13.35</v>
+        <v>76.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>64.87818030058806</v>
+        <v>45.73771227544637</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30.46784232992091</v>
+        <v>23.23611576927393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8458273144833002</v>
+        <v>0.3490207061623582</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1772137282984385</v>
+        <v>-0.054507722425839</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6163</v>
+        <v>6418</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>393.6329101980024</v>
+        <v>403.6595016422124</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>42.85</v>
+        <v>34.35</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.8630424759213</v>
+        <v>50.11611112603979</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.00064686519759</v>
+        <v>31.32351564039217</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.207447361020681</v>
+        <v>0.6413333463951123</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2430981603007811</v>
+        <v>-0.1532982065517019</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6192</v>
+        <v>6443</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>390.7200343177256</v>
+        <v>394.7930425375959</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>111.5</v>
+        <v>27.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.84633247326876</v>
+        <v>54.41790383168618</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>29.48916222908617</v>
+        <v>29.2138340510263</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8209899479094277</v>
+        <v>0.4616728907340448</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2354891531512986</v>
+        <v>0.2533259782828121</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6282</v>
+        <v>6163</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>378.89189001093</v>
+        <v>393.6329101980024</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>44.05</v>
+        <v>42.85</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.5653808630854</v>
+        <v>55.86304250124726</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.13699090420462</v>
+        <v>15.00064688661364</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.05991341916363</v>
+        <v>1.207447361020681</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.3118384232776854</v>
+        <v>0.2430981602674038</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6184</v>
+        <v>6192</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>367.8800903984031</v>
+        <v>390.7200343177254</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>40</v>
+        <v>111.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.76788523481834</v>
+        <v>47.84633229481121</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.15604151187099</v>
+        <v>29.48916222908618</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4157372629322765</v>
+        <v>0.8209899479094277</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0593403677745665</v>
+        <v>0.235489153262558</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6441</v>
+        <v>6282</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>366.6107158163426</v>
+        <v>378.89189001093</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>22.55</v>
+        <v>44.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.43799403409008</v>
+        <v>50.56538080713914</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.81271786491835</v>
+        <v>16.13699092899273</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2098376801582674</v>
+        <v>1.05991341916363</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.264809506778548</v>
+        <v>0.3118384234668409</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6188</v>
+        <v>6184</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>360.6438252941427</v>
+        <v>367.8800903984031</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.61559764780029</v>
+        <v>41.76788309318856</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.53202535773005</v>
+        <v>27.15604336612362</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9204820629043344</v>
+        <v>0.4157372629322765</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.2918913046391211</v>
+        <v>0.0593403689095371</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6277</v>
+        <v>6441</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>352.5105222935029</v>
+        <v>366.6107158163426</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>22.55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.32779069877108</v>
+        <v>43.43799398121232</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12.44131717029222</v>
+        <v>17.81271801966259</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5499145114771895</v>
+        <v>0.2098376801582674</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.07563103106404789</v>
+        <v>-0.2648095066895302</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6470</v>
+        <v>6188</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>350.1431669982019</v>
+        <v>360.6438252941426</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>42.8</v>
+        <v>62.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>49.97918397645706</v>
+        <v>41.61559815260992</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.05317319465644</v>
+        <v>26.53202530565017</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.25795072536873</v>
+        <v>0.9204820629043344</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0083462879852408</v>
+        <v>0.2918913041940407</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6435</v>
+        <v>6470</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>346.9162344981049</v>
+        <v>350.1431669982019</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>257</v>
+        <v>42.8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.09863161882433</v>
+        <v>49.97918405261606</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.84045171274681</v>
+        <v>20.05317328539646</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.424457295038883</v>
+        <v>1.25795072536873</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>2.816343132833389</v>
+        <v>0.008346288040875499</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6446</v>
+        <v>6435</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>345.5734318097288</v>
+        <v>346.9162344981047</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1205</v>
+        <v>257</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.28308753954867</v>
+        <v>51.09863159807458</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.43996440524338</v>
+        <v>16.84045172191334</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4744501910421428</v>
+        <v>1.424457295038883</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>3.494084303368744</v>
+        <v>2.816343132989165</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6237</v>
+        <v>6446</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>345.4181759909279</v>
+        <v>345.5734318097288</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>35.65</v>
+        <v>1205</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,49 +4845,49 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.54523109673051</v>
+        <v>46.28308751330174</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25.01057183398846</v>
+        <v>16.43996439012291</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5962489538921911</v>
+        <v>0.4744501910421428</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.08981447123374429</v>
+        <v>3.494084305594044</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6261</v>
+        <v>6237</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>343.0651328387323</v>
+        <v>345.4181759909293</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>35.65</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.6133947418183</v>
+        <v>52.54523138210239</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.22125475633058</v>
+        <v>25.01057188160675</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8320672925999428</v>
+        <v>0.5962489538921911</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1427096506236304</v>
+        <v>0.0898144714229096</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6279</v>
+        <v>6261</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>340.3469591780744</v>
+        <v>343.0651328387323</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>116</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.00808675516386</v>
+        <v>47.61339470365421</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>30.17681085831698</v>
+        <v>10.22125479911753</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.282459776375072</v>
+        <v>0.8320672925999428</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.9227973758537478</v>
+        <v>0.1427096508239181</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6236</v>
+        <v>6279</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>336.3294796956951</v>
+        <v>340.3469591780744</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.74956782292374</v>
+        <v>51.00808697649353</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.99815043752822</v>
+        <v>30.17681089865312</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0</v>
+        <v>1.282459776375072</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.560552563030408</v>
+        <v>0.9227973754086704</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6228</v>
+        <v>6236</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>330.9957914878494</v>
+        <v>336.3294796956951</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18.15</v>
+        <v>0</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>55.45378795790486</v>
+        <v>40.74956784498743</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.58896784158758</v>
+        <v>14.99815038433296</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.9769415774808968</v>
+        <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>1.027245491419966</v>
+        <v>-1.560552563597893</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6229</v>
+        <v>6228</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>328.1112380776374</v>
+        <v>330.9957914878491</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>23.9</v>
+        <v>18.15</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.10215121345279</v>
+        <v>55.45378795229247</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.3789327758506</v>
+        <v>14.58896787800369</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.29238094272924</v>
+        <v>0.9769415774808968</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0523374897968202</v>
+        <v>1.027245491408839</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6220</v>
+        <v>6229</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>325.6576276577721</v>
+        <v>328.1112380776374</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.65</v>
+        <v>23.9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>50.70856734677585</v>
+        <v>52.10215121345279</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.2791626064758</v>
+        <v>19.37893273681875</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.241202815099168</v>
+        <v>1.29238094272924</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1161257718657581</v>
+        <v>0.0523374897523127</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,41 +5191,41 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6167</v>
+        <v>6220</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>323.4744112284326</v>
+        <v>325.6576276577729</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10.3</v>
+        <v>25.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G90" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.77258349819975</v>
+        <v>50.70856743073826</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.0256997396764</v>
+        <v>13.27916284253842</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9922289282288724</v>
+        <v>1.241202815099168</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,51 +5234,51 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0238215500300403</v>
+        <v>0.1161257718212481</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6244</v>
+        <v>6167</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>322.1330574757565</v>
+        <v>323.4744112284326</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>22.8</v>
+        <v>10.3</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G91" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.24246337302161</v>
+        <v>48.77258362001601</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.30391012514048</v>
+        <v>14.02569975265882</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7388145261054365</v>
+        <v>0.9922289282288724</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0261871059052979</v>
+        <v>0.0238215499270617</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6465</v>
+        <v>6244</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>305.712649881272</v>
+        <v>322.1330574757565</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>41.2</v>
+        <v>22.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>37.90251130962472</v>
+        <v>44.24246343250911</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.05090110088868</v>
+        <v>18.30391015114883</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.055967796393282</v>
+        <v>0.7388145261054365</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1244248451778078</v>
+        <v>0.0261871059609362</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6223</v>
+        <v>6465</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>301.2364123052861</v>
+        <v>305.712649881272</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>5530</v>
+        <v>41.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.1409490517013</v>
+        <v>37.90251128564719</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.27041427007694</v>
+        <v>10.05090106472672</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8820010985153808</v>
+        <v>1.055967796393282</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,11 +5393,11 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>25.54717961323762</v>
+        <v>0.1244248451587388</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>293.9979886606804</v>
+        <v>295.1170862946692</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>888</v>
@@ -5431,10 +5431,10 @@
         <v>42.19358681055746</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13.76749398673771</v>
+        <v>13.76749405026401</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6872123473411823</v>
+        <v>0.8557326095521604</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>4.050455268601361</v>
+        <v>4.050455264150557</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.75030766912528</v>
+        <v>43.75030764726042</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.70966790737876</v>
+        <v>14.70966783013546</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.7992615305742037</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.20372210728192</v>
+        <v>48.20372200046686</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15.21983646921181</v>
+        <v>15.21983650567594</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.5159166195406477</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3397901506766164</v>
+        <v>0.3397901508991693</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>281.1273355486358</v>
+        <v>281.1273355486354</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>173</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.26287297184373</v>
+        <v>50.26287291986345</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.57129210923436</v>
+        <v>14.57129199487477</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.8932719272073454</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.3862135695008086</v>
+        <v>0.3862135702908507</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>273.1752717929261</v>
+        <v>273.1752717929269</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>12.65</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.62637103052138</v>
+        <v>46.62637041601838</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.37787590288776</v>
+        <v>21.37787590300966</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5962739456880218</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0135480195771423</v>
+        <v>-0.0135480193657249</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.70378022355504</v>
+        <v>44.70378021852532</v>
       </c>
       <c r="I99" s="2" t="n">
         <v>8.122052076412508</v>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6235</v>
+        <v>6272</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>228.1101545000344</v>
+        <v>242.2086852225574</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>36.7</v>
+        <v>25.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.28409538532568</v>
+        <v>45.85108083081201</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.12889763770266</v>
+        <v>21.54219532969888</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.860782091857923</v>
+        <v>0.3409582059973344</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1409603836958588</v>
+        <v>-0.1715473151547747</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6474</v>
+        <v>6235</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>226.8466930562406</v>
+        <v>228.1101545000344</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>35.55</v>
+        <v>36.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.26589077135909</v>
+        <v>36.28409608142226</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.89888117987769</v>
+        <v>16.12889765516014</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.351049755940078</v>
+        <v>1.860782091857923</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1112714090929575</v>
+        <v>-0.1409603835178274</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6176</v>
+        <v>6474</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>224.1783022428156</v>
+        <v>226.8466930562406</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>35.55</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.77287731122584</v>
+        <v>42.26589152711719</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.28958294960045</v>
+        <v>13.89888118815046</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4107090162559312</v>
+        <v>1.351049755940078</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2432599955613549</v>
+        <v>0.1112714087146328</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6272</v>
+        <v>6176</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>222.2086852225574</v>
+        <v>224.1783022428156</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>25.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.85108066881811</v>
+        <v>48.77287731122584</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.54219532477828</v>
+        <v>13.28958292999518</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3409582059973344</v>
+        <v>0.4107090162559312</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,11 +5976,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1715473146651855</v>
+        <v>-0.2432599949892583</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.17838387190766</v>
+        <v>44.17838379830267</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>27.23844007313665</v>
+        <v>27.23844014691709</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.3118183256896076</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0193443691094087</v>
+        <v>-0.0193443689981324</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.80452627818957</v>
+        <v>46.80452627625367</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>20.10480584427422</v>
+        <v>20.10480582330406</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.7146851779298677</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0758065775376459</v>
+        <v>-0.07580657751539251</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>212.4337802518634</v>
+        <v>212.4337802518635</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>91.40000000000001</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.91922566633703</v>
+        <v>47.91922578543535</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.197319508410246</v>
+        <v>9.197319586925319</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>1.611561632882907</v>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>212.059068696656</v>
+        <v>212.0590686966824</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>50.9</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.22892972719482</v>
+        <v>44.22892964154275</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.57037138436732</v>
+        <v>10.57037141551927</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.374019570346747</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0134714258961138</v>
+        <v>-0.0134714258516005</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>206.8882002268874</v>
+        <v>206.8882002268873</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>45.9</v>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.0078575027817</v>
+        <v>43.00785748350999</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.40234114617892</v>
+        <v>13.40234110681909</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.456920146231517</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1605652686070172</v>
+        <v>-0.1605652684067282</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>201.8974365640917</v>
+        <v>201.8974365640919</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>49</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.4701299047393</v>
+        <v>46.47012986972926</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>9.382210498088348</v>
+        <v>9.382210448323448</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.3182173801195025</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0600827524689053</v>
+        <v>0.0600827525245428</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.60285720000446</v>
+        <v>44.60285680447419</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.579611929862553</v>
+        <v>8.579611926854763</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.416240309454493</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1044186653463888</v>
+        <v>0.1044186654131521</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.5606574242953</v>
+        <v>46.56065758458215</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>9.593535430085852</v>
+        <v>9.593535533693656</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.939345514867798</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.076511913574065</v>
+        <v>0.07651191257261999</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45.69352033058559</v>
+        <v>45.69352018353486</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.40220130493803</v>
+        <v>19.40220141759241</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.6826799322072407</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0381078371717288</v>
+        <v>0.0381078372162395</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>52.2730811380327</v>
+        <v>52.27308114112744</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.675261296483735</v>
+        <v>7.675261335440338</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.0616233220572709</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.2111070406913459</v>
+        <v>0.2111070406690923</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>84.1512018174683</v>
+        <v>104.1512018174683</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>18.95</v>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.76124957436255</v>
+        <v>44.7612490603735</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.74096114501615</v>
+        <v>17.74096160688372</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.3114303476066001</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0896930564639957</v>
+        <v>0.0896930568200652</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>44.78221804078018</v>
+        <v>44.78221804078012</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>19.2</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>50.82249722659403</v>
+        <v>50.82249718503322</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.44968117379819</v>
+        <v>17.44968117415417</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.9970592216165668</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0896345531326838</v>
+        <v>-0.08963455322170159</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
